--- a/data/PipeSpec_Master.xlsx
+++ b/data/PipeSpec_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\theis\Documents\PipingIQ\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A96A651-CD5A-4347-B5EF-F1766E718C25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83E835E2-938F-4B28-B9F0-41C5CF6A5610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="75450" yWindow="825" windowWidth="21600" windowHeight="11295" xr2:uid="{D2C3A356-DDB6-41C6-B489-C16F7A9063F9}"/>
+    <workbookView xWindow="1980" yWindow="780" windowWidth="16890" windowHeight="11633" xr2:uid="{D2C3A356-DDB6-41C6-B489-C16F7A9063F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="290">
   <si>
     <t>Service</t>
   </si>
@@ -470,9 +470,6 @@
 SOCKET WELD:  ANSI B16.11, SCHEDULE 40 ASTM A105 STEEL</t>
   </si>
   <si>
-    <t xml:space="preserve">MAXIMUM TEMPERATURE (F):                                                                  MAXIMUM PRESSURE (PSI)(1):  </t>
-  </si>
-  <si>
     <t>PIQ CS-05</t>
   </si>
   <si>
@@ -573,9 +570,6 @@
   </si>
   <si>
     <t>ASTM B75 SEAMLESS WROUGHT COPPER</t>
-  </si>
-  <si>
-    <t>Jacket/Armour</t>
   </si>
   <si>
     <t>JACKET:  ASTM D1047 PVC, FLAME RETARDANT    ARMOR:  FLEXIBLE, INTERLOCKING GALVANIZED STEEL</t>
@@ -1502,16 +1496,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{606A2799-9269-4925-B09A-0C30E8609271}">
-  <dimension ref="A1:AE66"/>
-  <sheetFormatPr defaultRowHeight="49.9" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AE64"/>
+  <sheetFormatPr defaultRowHeight="49.9" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="9" width="60.7109375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="60.7109375" style="9" customWidth="1"/>
-    <col min="11" max="26" width="60.7109375" style="1" customWidth="1"/>
-    <col min="27" max="211" width="60.7109375" customWidth="1"/>
+    <col min="1" max="9" width="60.73046875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="60.73046875" style="9" customWidth="1"/>
+    <col min="11" max="26" width="60.73046875" style="1" customWidth="1"/>
+    <col min="27" max="211" width="60.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="1.05">
       <c r="A1" s="6" t="s">
         <v>74</v>
       </c>
@@ -1519,7 +1513,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>10</v>
@@ -1552,7 +1546,7 @@
         <v>58</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O1" s="6" t="s">
         <v>13</v>
@@ -1570,51 +1564,51 @@
         <v>66</v>
       </c>
       <c r="T1" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="U1" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="V1" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="W1" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="X1" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="Y1" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="Z1" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="AA1" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="AB1" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="AC1" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="AD1" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="V1" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="W1" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="X1" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="Y1" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="Z1" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="AA1" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="AB1" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="AC1" s="12" t="s">
+      <c r="AE1" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="AD1" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="AE1" s="12" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="2" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>95</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>22</v>
@@ -1638,7 +1632,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>50</v>
@@ -1659,18 +1653,18 @@
         <v>116</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>95</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>17</v>
@@ -1694,7 +1688,7 @@
         <v>47</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>50</v>
@@ -1712,15 +1706,15 @@
         <v>116</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>94</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>7</v>
@@ -1744,7 +1738,7 @@
         <v>40</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>35</v>
@@ -1765,15 +1759,15 @@
         <v>116</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>93</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>7</v>
@@ -1818,10 +1812,10 @@
         <v>116</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="6" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>92</v>
       </c>
@@ -1829,7 +1823,7 @@
         <v>27</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>22</v>
@@ -1868,10 +1862,10 @@
         <v>116</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="7" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>92</v>
       </c>
@@ -1879,7 +1873,7 @@
         <v>27</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>17</v>
@@ -1918,10 +1912,10 @@
         <v>116</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>90</v>
       </c>
@@ -1929,7 +1923,7 @@
         <v>56</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>22</v>
@@ -1959,10 +1953,10 @@
         <v>116</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>91</v>
       </c>
@@ -1970,7 +1964,7 @@
         <v>56</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>17</v>
@@ -2000,10 +1994,10 @@
         <v>116</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>89</v>
       </c>
@@ -2050,10 +2044,10 @@
         <v>116</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>88</v>
       </c>
@@ -2100,18 +2094,18 @@
         <v>116</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="12" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>118</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>73</v>
@@ -2132,7 +2126,7 @@
         <v>81</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>83</v>
@@ -2153,18 +2147,18 @@
         <v>116</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>17</v>
@@ -2185,7 +2179,7 @@
         <v>82</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>84</v>
@@ -2209,10 +2203,10 @@
         <v>116</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="14" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>119</v>
       </c>
@@ -2220,7 +2214,7 @@
         <v>96</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>73</v>
@@ -2241,7 +2235,7 @@
         <v>100</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="K14" s="5" t="s">
         <v>83</v>
@@ -2259,10 +2253,10 @@
         <v>116</v>
       </c>
       <c r="U14" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
         <v>119</v>
       </c>
@@ -2270,7 +2264,7 @@
         <v>96</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>17</v>
@@ -2291,7 +2285,7 @@
         <v>101</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K15" s="5" t="s">
         <v>84</v>
@@ -2309,10 +2303,10 @@
         <v>116</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="16" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>120</v>
       </c>
@@ -2320,7 +2314,7 @@
         <v>103</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>73</v>
@@ -2341,7 +2335,7 @@
         <v>107</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>111</v>
@@ -2359,10 +2353,10 @@
         <v>116</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
         <v>120</v>
       </c>
@@ -2370,7 +2364,7 @@
         <v>103</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>17</v>
@@ -2391,7 +2385,7 @@
         <v>108</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>111</v>
@@ -2409,18 +2403,18 @@
         <v>116</v>
       </c>
       <c r="U17" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
         <v>92</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>73</v>
@@ -2441,7 +2435,7 @@
         <v>121</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K18" s="1" t="s">
         <v>83</v>
@@ -2459,18 +2453,18 @@
         <v>116</v>
       </c>
       <c r="U18" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
         <v>92</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>17</v>
@@ -2491,7 +2485,7 @@
         <v>101</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>84</v>
@@ -2500,7 +2494,7 @@
         <v>112</v>
       </c>
       <c r="O19" s="11" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="R19" s="1" t="s">
         <v>87</v>
@@ -2509,24 +2503,24 @@
         <v>116</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="C20" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>73</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>8</v>
@@ -2535,48 +2529,48 @@
         <v>107</v>
       </c>
       <c r="H20" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="J20" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="K20" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="J20" s="11" t="s">
-        <v>210</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>129</v>
       </c>
       <c r="L20" s="1" t="s">
         <v>112</v>
       </c>
       <c r="O20" s="11" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="R20" s="1" t="s">
         <v>114</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="U20" s="1" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="C21" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>6</v>
@@ -2591,16 +2585,16 @@
         <v>101</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L21" s="1" t="s">
         <v>112</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="R21" s="1" t="s">
         <v>114</v>
@@ -2609,27 +2603,27 @@
         <v>19</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>73</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>8</v>
@@ -2644,45 +2638,45 @@
         <v>81</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L22" s="1" t="s">
         <v>112</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="S22" s="1" t="s">
         <v>19</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="U22" s="1" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>8</v>
@@ -2697,69 +2691,69 @@
         <v>101</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L23" s="1" t="s">
         <v>112</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="S23" s="1" t="s">
         <v>19</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="U23" s="1" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>73</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>6</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H24" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="I24" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="I24" s="1" t="s">
-        <v>138</v>
-      </c>
       <c r="J24" s="9" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L24" s="1" t="s">
         <v>112</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="R24" s="1" t="s">
         <v>87</v>
@@ -2768,51 +2762,51 @@
         <v>19</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="U24" s="1" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>6</v>
       </c>
       <c r="G25" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="I25" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="H25" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>145</v>
-      </c>
       <c r="J25" s="9" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L25" s="1" t="s">
         <v>112</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="R25" s="1" t="s">
         <v>87</v>
@@ -2821,437 +2815,427 @@
         <v>19</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="U25" s="1" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>73</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="T26" s="1" t="s">
         <v>116</v>
       </c>
       <c r="U26" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="T27" s="1" t="s">
         <v>116</v>
       </c>
       <c r="U27" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>73</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="T28" s="1" t="s">
         <v>116</v>
       </c>
       <c r="U28" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E29" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="T29" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="U29" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="H29" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="J29" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="N29" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="T29" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="U29" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>170</v>
-      </c>
       <c r="C30" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>73</v>
       </c>
       <c r="E30" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="T30" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="U30" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="H30" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="J30" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="N30" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="T30" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="U30" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="B31" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="T31" s="1" t="s">
         <v>116</v>
       </c>
       <c r="U31" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>73</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="T32" s="1" t="s">
         <v>116</v>
       </c>
       <c r="U32" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="33" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="33" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="T33" s="1" t="s">
         <v>116</v>
       </c>
       <c r="U33" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="34" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="J34" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="K34" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="L34" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="M34" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="N34" s="6" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="34" spans="1:31" ht="58.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J34" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="N34" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="O34" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="P34" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q34" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="R34" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="S34" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="T34" s="6"/>
-      <c r="U34" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="V34" s="6" t="s">
+      <c r="R34" s="1" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="35" spans="1:31" ht="58.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V34" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="35" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>161</v>
+        <v>190</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>73</v>
       </c>
       <c r="E35" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="H35" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="H35" s="1" t="s">
+      <c r="J35" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="R35" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="V35" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="J35" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="R35" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="V35" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="36" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
-        <v>155</v>
+        <v>118</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>73</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>156</v>
+        <v>75</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="J36" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="N36" s="1" t="s">
-        <v>149</v>
+        <v>79</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="R36" s="1" t="s">
-        <v>160</v>
+        <v>87</v>
+      </c>
+      <c r="S36" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U36" s="1" t="s">
+        <v>116</v>
       </c>
       <c r="V36" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="37" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="37" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
         <v>118</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L37" s="1" t="s">
         <v>112</v>
       </c>
+      <c r="M37" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="O37" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="R37" s="1" t="s">
         <v>87</v>
@@ -3263,51 +3247,48 @@
         <v>116</v>
       </c>
       <c r="V37" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="38" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="38" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
-        <v>118</v>
+        <v>194</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J38" s="9" t="s">
-        <v>247</v>
+        <v>81</v>
+      </c>
+      <c r="J38" s="11" t="s">
+        <v>207</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L38" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="M38" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="O38" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R38" s="1" t="s">
         <v>87</v>
@@ -3319,48 +3300,51 @@
         <v>116</v>
       </c>
       <c r="V38" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="39" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="39" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="J39" s="11" t="s">
-        <v>209</v>
+        <v>82</v>
+      </c>
+      <c r="J39" s="9" t="s">
+        <v>245</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>112</v>
       </c>
+      <c r="M39" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="O39" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="R39" s="1" t="s">
         <v>87</v>
@@ -3372,92 +3356,89 @@
         <v>116</v>
       </c>
       <c r="V39" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="40" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="40" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
-        <v>196</v>
+        <v>94</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="D40" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J40" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O40" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="P40" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="R40" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="U40" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="V40" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="41" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A41" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J40" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="M40" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="O40" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="R40" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="S40" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U40" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="V40" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="41" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="E41" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J41" s="9" t="s">
         <v>41</v>
@@ -3472,7 +3453,7 @@
         <v>36</v>
       </c>
       <c r="P41" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="R41" s="1" t="s">
         <v>116</v>
@@ -3481,424 +3462,406 @@
         <v>116</v>
       </c>
       <c r="V41" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="42" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D42" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="42" spans="1:31" s="17" customFormat="1" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A42" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="I42" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="J42" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="K42" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="L42" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="M42" s="9"/>
+      <c r="N42" s="9"/>
+      <c r="O42" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="P42" s="9"/>
+      <c r="Q42" s="9"/>
+      <c r="R42" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="S42" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="T42" s="9"/>
+      <c r="U42" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="V42" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="W42" s="9"/>
+      <c r="X42" s="9"/>
+      <c r="Y42" s="9"/>
+      <c r="Z42" s="9"/>
+    </row>
+    <row r="43" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A43" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E42" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J42" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="L42" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="P42" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="R42" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="U42" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="V42" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="43" spans="1:31" s="17" customFormat="1" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="B43" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="D43" s="9" t="s">
+      <c r="E43" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J43" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="R43" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="S43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U43" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="V43" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="44" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A44" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E43" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F43" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="G43" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="I43" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="J43" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="K43" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="L43" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="M43" s="9"/>
-      <c r="N43" s="9"/>
-      <c r="O43" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="P43" s="9"/>
-      <c r="Q43" s="9"/>
-      <c r="R43" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="S43" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="T43" s="9"/>
-      <c r="U43" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="V43" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="W43" s="9"/>
-      <c r="X43" s="9"/>
-      <c r="Y43" s="9"/>
-      <c r="Z43" s="9"/>
-    </row>
-    <row r="44" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="E44" s="1" t="s">
-        <v>76</v>
+        <v>229</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G44" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>82</v>
+      <c r="G44" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="H44" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="I44" s="13" t="s">
+        <v>230</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>84</v>
+        <v>234</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="M44" s="1" t="s">
-        <v>64</v>
+        <v>236</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>86</v>
+        <v>242</v>
       </c>
       <c r="R44" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="S44" s="1" t="s">
-        <v>19</v>
+      <c r="T44" s="1" t="s">
+        <v>237</v>
       </c>
       <c r="U44" s="1" t="s">
-        <v>116</v>
+        <v>238</v>
       </c>
       <c r="V44" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="45" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>244</v>
+      </c>
+      <c r="Y44" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="AE44" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="45" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>231</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G45" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="H45" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="I45" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="J45" s="9" t="s">
-        <v>248</v>
+      <c r="G45" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J45" s="18" t="s">
+        <v>247</v>
       </c>
       <c r="K45" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="L45" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="L45" s="1" t="s">
-        <v>238</v>
-      </c>
       <c r="O45" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="R45" s="1" t="s">
         <v>87</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="U45" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="Y45" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="V45" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="Y45" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="AE45" s="1" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="46" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AE45" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="46" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A46" s="1" t="s">
-        <v>229</v>
+        <v>273</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>135</v>
+        <v>261</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>231</v>
+        <v>272</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>6</v>
+        <v>262</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>233</v>
+        <v>271</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>235</v>
+        <v>264</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="J46" s="18" t="s">
-        <v>249</v>
+        <v>265</v>
+      </c>
+      <c r="J46" s="9" t="s">
+        <v>270</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>237</v>
+        <v>266</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="O46" s="1" t="s">
-        <v>245</v>
+        <v>236</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="O46" s="15" t="s">
+        <v>268</v>
       </c>
       <c r="R46" s="1" t="s">
         <v>87</v>
       </c>
+      <c r="S46" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="T46" s="1" t="s">
-        <v>239</v>
+        <v>19</v>
       </c>
       <c r="U46" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="Y46" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="AE46" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="47" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C47" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="V46" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="47" spans="1:31" s="16" customFormat="1" ht="49.9" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A47" s="19" t="s">
+        <v>273</v>
+      </c>
+      <c r="B47" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="C47" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F47" s="15" t="s">
         <v>263</v>
       </c>
-      <c r="D47" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="F47" s="1" t="s">
+      <c r="G47" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="H47" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="G47" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="H47" s="1" t="s">
+      <c r="I47" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="J47" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="K47" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="I47" s="1" t="s">
+      <c r="L47" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="M47" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="J47" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="K47" s="1" t="s">
+      <c r="N47" s="15"/>
+      <c r="O47" s="15" t="s">
         <v>268</v>
       </c>
-      <c r="L47" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="M47" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="O47" s="15" t="s">
-        <v>270</v>
-      </c>
+      <c r="P47" s="15"/>
+      <c r="Q47" s="15"/>
       <c r="R47" s="1" t="s">
         <v>87</v>
       </c>
       <c r="S47" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="T47" s="1" t="s">
+      <c r="T47" s="15"/>
+      <c r="U47" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="V47" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="W47" s="15"/>
+      <c r="X47" s="15"/>
+      <c r="Y47" s="15"/>
+      <c r="Z47" s="15"/>
+    </row>
+    <row r="48" spans="1:31" ht="49.9" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A48" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="G48" t="s">
+        <v>278</v>
+      </c>
+      <c r="H48" t="s">
+        <v>279</v>
+      </c>
+      <c r="I48" t="s">
+        <v>277</v>
+      </c>
+      <c r="O48" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="U47" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="V47" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="48" spans="1:31" s="16" customFormat="1" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="19" t="s">
+      <c r="R48" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="S48" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" ht="49.9" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A49" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>275</v>
-      </c>
-      <c r="B48" s="19" t="s">
-        <v>262</v>
-      </c>
-      <c r="C48" s="19" t="s">
-        <v>263</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="F48" s="15" t="s">
-        <v>265</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="J48" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="K48" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="L48" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="M48" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="N48" s="15"/>
-      <c r="O48" s="15" t="s">
-        <v>270</v>
-      </c>
-      <c r="P48" s="15"/>
-      <c r="Q48" s="15"/>
-      <c r="R48" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="S48" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="T48" s="15"/>
-      <c r="U48" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="V48" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="W48" s="15"/>
-      <c r="X48" s="15"/>
-      <c r="Y48" s="15"/>
-      <c r="Z48" s="15"/>
-    </row>
-    <row r="49" spans="1:22" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>277</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>29</v>
@@ -3907,16 +3870,16 @@
         <v>73</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="G49" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="H49" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="I49" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="O49" s="15" t="s">
         <v>19</v>
@@ -3928,141 +3891,44 @@
         <v>19</v>
       </c>
     </row>
-    <row r="50" spans="1:22" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>276</v>
-      </c>
+    <row r="50" spans="1:19" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B50" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E50" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G50" t="s">
-        <v>278</v>
-      </c>
-      <c r="H50" t="s">
-        <v>279</v>
-      </c>
-      <c r="I50" t="s">
-        <v>279</v>
-      </c>
-      <c r="O50" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="R50" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="S50" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="51" spans="1:22" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="1" t="s">
+    </row>
+    <row r="52" spans="1:19" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B52" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B54" s="1" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="53" spans="1:22" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="1" t="s">
+    <row r="56" spans="1:19" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B56" s="1" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="55" spans="1:22" ht="49.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="F55" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G55" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="H55" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I55" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="J55" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="K55" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="L55" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="M55" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="N55" s="6"/>
-      <c r="O55" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="P55" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q55" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="R55" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="S55" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="T55" s="6"/>
-      <c r="U55" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="V55" s="6"/>
-    </row>
-    <row r="56" spans="1:22" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="1" t="s">
+    <row r="58" spans="1:19" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B58" s="1" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="58" spans="1:22" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="1" t="s">
+    <row r="60" spans="1:19" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B60" s="1" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="60" spans="1:22" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="1" t="s">
+    <row r="62" spans="1:19" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B62" s="1" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="62" spans="1:22" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="1" t="s">
+    <row r="64" spans="1:19" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B64" s="1" t="s">
         <v>289</v>
-      </c>
-    </row>
-    <row r="64" spans="1:22" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="1" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="66" spans="2:2" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="1" t="s">
-        <v>291</v>
       </c>
     </row>
   </sheetData>
